--- a/utils/reference/volare_bpi_cards_xdays-header.xlsx
+++ b/utils/reference/volare_bpi_cards_xdays-header.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12180"/>
+    <workbookView windowWidth="27945" windowHeight="11460"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,165 +32,171 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="85">
   <si>
+    <t>CH CODE</t>
+  </si>
+  <si>
+    <t>CUST_ID</t>
+  </si>
+  <si>
+    <t>CUST_NAME</t>
+  </si>
+  <si>
+    <t>AOD</t>
+  </si>
+  <si>
+    <t>QUEUE</t>
+  </si>
+  <si>
+    <t>OFC</t>
+  </si>
+  <si>
+    <t>HOME</t>
+  </si>
+  <si>
+    <t>MOBILE_NO</t>
+  </si>
+  <si>
+    <t>TU</t>
+  </si>
+  <si>
+    <t>ADDRESS</t>
+  </si>
+  <si>
+    <t>EMAIL</t>
+  </si>
+  <si>
+    <t>GENDER</t>
+  </si>
+  <si>
+    <t>TCL</t>
+  </si>
+  <si>
+    <t>BOS</t>
+  </si>
+  <si>
+    <t>MAD</t>
+  </si>
+  <si>
+    <t>PDA</t>
+  </si>
+  <si>
+    <t>LAST PAYMENT AMOUNT</t>
+  </si>
+  <si>
+    <t>LAST_PAYMENT_DATE</t>
+  </si>
+  <si>
+    <t>DELINQUENCY_STRING</t>
+  </si>
+  <si>
+    <t>ADA_ACCOUNT</t>
+  </si>
+  <si>
+    <t>DEBIT_AMOUNT_PREFERENCE</t>
+  </si>
+  <si>
+    <t>UNIT_CODE</t>
+  </si>
+  <si>
+    <t>HO FLAG</t>
+  </si>
+  <si>
+    <t>BIRTHDATE</t>
+  </si>
+  <si>
+    <t>BLOCK_CODE</t>
+  </si>
+  <si>
+    <t>MEMO_LINE</t>
+  </si>
+  <si>
+    <t>D_CUST_OPN</t>
+  </si>
+  <si>
+    <t>LAST DUE DATE</t>
+  </si>
+  <si>
+    <t>SPOUSE NUMBER</t>
+  </si>
+  <si>
+    <t>TYPE</t>
+  </si>
+  <si>
     <t>Ch Code</t>
   </si>
   <si>
-    <t>CUST_ID</t>
-  </si>
-  <si>
-    <t>CUST_NAME</t>
-  </si>
-  <si>
-    <t>AOD</t>
-  </si>
-  <si>
-    <t>QUEUE</t>
-  </si>
-  <si>
-    <t>OFC</t>
-  </si>
-  <si>
-    <t>HOME</t>
-  </si>
-  <si>
-    <t>MOBILE_NO</t>
-  </si>
-  <si>
-    <t>TU</t>
-  </si>
-  <si>
-    <t>ADDRESS</t>
-  </si>
-  <si>
-    <t>EMAIL</t>
-  </si>
-  <si>
-    <t>GENDER</t>
-  </si>
-  <si>
-    <t>TCL</t>
-  </si>
-  <si>
-    <t>BOS</t>
-  </si>
-  <si>
-    <t>MAD</t>
-  </si>
-  <si>
-    <t>PDA</t>
-  </si>
-  <si>
-    <t>LAST PAYMENT AMOUNT</t>
-  </si>
-  <si>
-    <t>LAST_PAYMENT_DATE</t>
-  </si>
-  <si>
-    <t>DELINQUENCY_STRING</t>
-  </si>
-  <si>
-    <t>ADA_ACCOUNT</t>
-  </si>
-  <si>
-    <t>DEBIT_AMOUNT_PREFERENCE</t>
-  </si>
-  <si>
-    <t>UNIT_CODE</t>
-  </si>
-  <si>
-    <t>HO FLAG</t>
-  </si>
-  <si>
-    <t>BIRTHDATE</t>
+    <t>cust_id</t>
+  </si>
+  <si>
+    <t>cust_name</t>
+  </si>
+  <si>
+    <t>aod</t>
+  </si>
+  <si>
+    <t>queue</t>
+  </si>
+  <si>
+    <t>ofc</t>
+  </si>
+  <si>
+    <t>home</t>
+  </si>
+  <si>
+    <t>mobile_no</t>
+  </si>
+  <si>
+    <t>tu</t>
+  </si>
+  <si>
+    <t>address</t>
+  </si>
+  <si>
+    <t>email</t>
+  </si>
+  <si>
+    <t>gender</t>
+  </si>
+  <si>
+    <t>tcl</t>
+  </si>
+  <si>
+    <t>bos</t>
+  </si>
+  <si>
+    <t>mad</t>
+  </si>
+  <si>
+    <t>pda</t>
+  </si>
+  <si>
+    <t>last payment amount</t>
+  </si>
+  <si>
+    <t>last_payment_date</t>
+  </si>
+  <si>
+    <t>delinquency_string</t>
+  </si>
+  <si>
+    <t>ada_account</t>
+  </si>
+  <si>
+    <t>debit_amount_preference</t>
+  </si>
+  <si>
+    <t>unit_code</t>
+  </si>
+  <si>
+    <t>ho flag</t>
+  </si>
+  <si>
+    <t>birthdate</t>
   </si>
   <si>
     <t>block_code</t>
   </si>
   <si>
-    <t>MEMO_LINE</t>
-  </si>
-  <si>
-    <t>D_CUST_OPN</t>
-  </si>
-  <si>
-    <t>LAST DUE DATE</t>
-  </si>
-  <si>
-    <t>SPOUSE NUMBER</t>
-  </si>
-  <si>
-    <t>TYPE</t>
-  </si>
-  <si>
-    <t>cust_id</t>
-  </si>
-  <si>
-    <t>cust_name</t>
-  </si>
-  <si>
-    <t>aod</t>
-  </si>
-  <si>
-    <t>queue</t>
-  </si>
-  <si>
-    <t>ofc</t>
-  </si>
-  <si>
-    <t>home</t>
-  </si>
-  <si>
-    <t>mobile_no</t>
-  </si>
-  <si>
-    <t>tu</t>
-  </si>
-  <si>
-    <t>address</t>
-  </si>
-  <si>
-    <t>email</t>
-  </si>
-  <si>
-    <t>gender</t>
-  </si>
-  <si>
-    <t>tcl</t>
-  </si>
-  <si>
-    <t>bos</t>
-  </si>
-  <si>
-    <t>mad</t>
-  </si>
-  <si>
-    <t>pda</t>
-  </si>
-  <si>
-    <t>last payment amount</t>
-  </si>
-  <si>
-    <t>last_payment_date</t>
-  </si>
-  <si>
-    <t>delinquency_string</t>
-  </si>
-  <si>
-    <t>ada_account</t>
-  </si>
-  <si>
-    <t>debit_amount_preference</t>
-  </si>
-  <si>
-    <t>unit_code</t>
-  </si>
-  <si>
-    <t>ho flag</t>
-  </si>
-  <si>
-    <t>birthdate</t>
-  </si>
-  <si>
     <t>memo_line</t>
   </si>
   <si>
@@ -206,9 +212,6 @@
     <t>type</t>
   </si>
   <si>
-    <t>CH CODE</t>
-  </si>
-  <si>
     <t>CUSTOMER ID</t>
   </si>
   <si>
@@ -243,9 +246,6 @@
   </si>
   <si>
     <t>HOLD_OUT_F</t>
-  </si>
-  <si>
-    <t>BLOCK_CODE</t>
   </si>
   <si>
     <t>customer id</t>
@@ -458,7 +458,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -593,12 +593,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -636,12 +630,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -883,54 +871,51 @@
     <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="58" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1464,8 +1449,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AD6"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="5"/>
+  <dimension ref="A1:AD5"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="4"/>
   <cols>
     <col min="2" max="2" width="13.1428571428571" customWidth="1"/>
     <col min="3" max="4" width="12.1428571428571" customWidth="1"/>
@@ -1504,34 +1489,34 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
       <c r="M1" s="1" t="s">
@@ -1549,422 +1534,300 @@
       <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="5" t="s">
+      <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="V1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="W1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="5" t="s">
+      <c r="X1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="Y1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="5" t="s">
+      <c r="AA1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="5" t="s">
+      <c r="AB1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AC1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AD1" s="1" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:30">
-      <c r="A2" s="1" t="str">
-        <f>UPPER(A1)</f>
-        <v>CH CODE</v>
-      </c>
-      <c r="B2" s="1" t="str">
-        <f t="shared" ref="B2:AD2" si="0">UPPER(B1)</f>
-        <v>CUST_ID</v>
-      </c>
-      <c r="C2" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>CUST_NAME</v>
-      </c>
-      <c r="D2" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>AOD</v>
-      </c>
-      <c r="E2" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>QUEUE</v>
-      </c>
-      <c r="F2" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>OFC</v>
-      </c>
-      <c r="G2" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>HOME</v>
-      </c>
-      <c r="H2" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>MOBILE_NO</v>
-      </c>
-      <c r="I2" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>TU</v>
-      </c>
-      <c r="J2" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>ADDRESS</v>
-      </c>
-      <c r="K2" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>EMAIL</v>
-      </c>
-      <c r="L2" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>GENDER</v>
-      </c>
-      <c r="M2" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>TCL</v>
-      </c>
-      <c r="N2" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>BOS</v>
-      </c>
-      <c r="O2" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>MAD</v>
-      </c>
-      <c r="P2" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>PDA</v>
-      </c>
-      <c r="Q2" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>LAST PAYMENT AMOUNT</v>
-      </c>
-      <c r="R2" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>LAST_PAYMENT_DATE</v>
-      </c>
-      <c r="S2" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>DELINQUENCY_STRING</v>
-      </c>
-      <c r="T2" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>ADA_ACCOUNT</v>
-      </c>
-      <c r="U2" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>DEBIT_AMOUNT_PREFERENCE</v>
-      </c>
-      <c r="V2" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>UNIT_CODE</v>
-      </c>
-      <c r="W2" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>HO FLAG</v>
-      </c>
-      <c r="X2" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>BIRTHDATE</v>
-      </c>
-      <c r="Y2" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>BLOCK_CODE</v>
-      </c>
-      <c r="Z2" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>MEMO_LINE</v>
-      </c>
-      <c r="AA2" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>D_CUST_OPN</v>
-      </c>
-      <c r="AB2" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>LAST DUE DATE</v>
-      </c>
-      <c r="AC2" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>SPOUSE NUMBER</v>
-      </c>
-      <c r="AD2" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>TYPE</v>
+      <c r="A2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="W2" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="X2" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y2" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z2" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="AA2" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AB2" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AC2" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="AD2" s="2" t="s">
+        <v>59</v>
       </c>
     </row>
-    <row r="3" spans="1:30">
-      <c r="A3" s="4" t="s">
+    <row r="3" spans="1:27">
+      <c r="A3" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="L3" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="M3" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="O3" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="P3" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q3" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="R3" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="S3" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="T3" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="U3" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="V3" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="W3" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="X3" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="Y3" s="4" t="s">
+      <c r="B3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F3" t="s">
+        <v>62</v>
+      </c>
+      <c r="G3" t="s">
+        <v>63</v>
+      </c>
+      <c r="H3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I3" t="s">
+        <v>64</v>
+      </c>
+      <c r="J3" t="s">
+        <v>65</v>
+      </c>
+      <c r="K3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M3" t="s">
+        <v>66</v>
+      </c>
+      <c r="N3" t="s">
+        <v>13</v>
+      </c>
+      <c r="O3" t="s">
+        <v>14</v>
+      </c>
+      <c r="P3" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>68</v>
+      </c>
+      <c r="R3" t="s">
+        <v>17</v>
+      </c>
+      <c r="S3" t="s">
+        <v>69</v>
+      </c>
+      <c r="T3" t="s">
+        <v>19</v>
+      </c>
+      <c r="V3" t="s">
+        <v>70</v>
+      </c>
+      <c r="W3" t="s">
+        <v>71</v>
+      </c>
+      <c r="X3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y3" t="s">
         <v>24</v>
       </c>
-      <c r="Z3" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="AA3" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="AB3" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="AC3" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="AD3" s="4" t="s">
-        <v>57</v>
+      <c r="Z3" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:27">
       <c r="A4" t="s">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="C4" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="D4" t="s">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="E4" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="F4" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="G4" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="H4" t="s">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="I4" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="J4" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="K4" t="s">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="L4" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="M4" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="N4" t="s">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="O4" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="P4" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="Q4" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="R4" t="s">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="S4" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="T4" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="V4" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="W4" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="X4" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="Y4" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="Z4" t="s">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="AA4" t="s">
-        <v>26</v>
+        <v>56</v>
       </c>
     </row>
-    <row r="5" spans="1:27">
-      <c r="A5" t="s">
-        <v>58</v>
-      </c>
-      <c r="B5" t="s">
-        <v>72</v>
-      </c>
-      <c r="C5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E5" t="s">
-        <v>73</v>
-      </c>
-      <c r="F5" t="s">
-        <v>74</v>
-      </c>
-      <c r="G5" t="s">
-        <v>75</v>
-      </c>
-      <c r="H5" t="s">
-        <v>36</v>
-      </c>
-      <c r="I5" t="s">
-        <v>76</v>
-      </c>
-      <c r="J5" t="s">
-        <v>77</v>
-      </c>
-      <c r="K5" t="s">
-        <v>39</v>
-      </c>
-      <c r="L5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M5" t="s">
-        <v>78</v>
-      </c>
-      <c r="N5" t="s">
-        <v>42</v>
-      </c>
-      <c r="O5" t="s">
-        <v>43</v>
-      </c>
-      <c r="P5" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>80</v>
-      </c>
+    <row r="5" spans="18:18">
       <c r="R5" t="s">
-        <v>46</v>
-      </c>
-      <c r="S5" t="s">
-        <v>81</v>
-      </c>
-      <c r="T5" t="s">
-        <v>48</v>
-      </c>
-      <c r="V5" t="s">
-        <v>82</v>
-      </c>
-      <c r="W5" t="s">
-        <v>83</v>
-      </c>
-      <c r="X5" t="s">
-        <v>52</v>
-      </c>
-      <c r="Y5" t="s">
-        <v>24</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>53</v>
-      </c>
-      <c r="AA5" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="6" spans="18:18">
-      <c r="R6" t="s">
         <v>84</v>
       </c>
     </row>

--- a/utils/reference/volare_bpi_cards_xdays-header.xlsx
+++ b/utils/reference/volare_bpi_cards_xdays-header.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11460"/>
+    <workbookView windowWidth="27945" windowHeight="12180"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="77">
   <si>
     <t>CH CODE</t>
   </si>
@@ -56,9 +56,6 @@
     <t>MOBILE_NO</t>
   </si>
   <si>
-    <t>TU</t>
-  </si>
-  <si>
     <t>ADDRESS</t>
   </si>
   <si>
@@ -116,12 +113,6 @@
     <t>LAST DUE DATE</t>
   </si>
   <si>
-    <t>SPOUSE NUMBER</t>
-  </si>
-  <si>
-    <t>TYPE</t>
-  </si>
-  <si>
     <t>Ch Code</t>
   </si>
   <si>
@@ -146,9 +137,6 @@
     <t>mobile_no</t>
   </si>
   <si>
-    <t>tu</t>
-  </si>
-  <si>
     <t>address</t>
   </si>
   <si>
@@ -206,12 +194,6 @@
     <t>last due date</t>
   </si>
   <si>
-    <t>spouse number</t>
-  </si>
-  <si>
-    <t>type</t>
-  </si>
-  <si>
     <t>CUSTOMER ID</t>
   </si>
   <si>
@@ -224,9 +206,6 @@
     <t>HOME_PH</t>
   </si>
   <si>
-    <t>TU_NUMBERS</t>
-  </si>
-  <si>
     <t>PRIMARY ADDRESS</t>
   </si>
   <si>
@@ -258,9 +237,6 @@
   </si>
   <si>
     <t>home_ph</t>
-  </si>
-  <si>
-    <t>tu_numbers</t>
   </si>
   <si>
     <t>primary address</t>
@@ -1449,7 +1425,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AD5"/>
+  <dimension ref="A1:AA5"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="4"/>
   <cols>
     <col min="2" max="2" width="13.1428571428571" customWidth="1"/>
@@ -1458,31 +1434,28 @@
     <col min="6" max="6" width="10.5714285714286" customWidth="1"/>
     <col min="7" max="7" width="6.57142857142857" customWidth="1"/>
     <col min="8" max="8" width="11.7142857142857" customWidth="1"/>
-    <col min="9" max="9" width="13.1428571428571" customWidth="1"/>
-    <col min="10" max="10" width="17.7142857142857" customWidth="1"/>
-    <col min="11" max="11" width="6.57142857142857" customWidth="1"/>
-    <col min="12" max="12" width="8.28571428571429" customWidth="1"/>
-    <col min="13" max="13" width="18.5714285714286" customWidth="1"/>
-    <col min="14" max="14" width="4.57142857142857" customWidth="1"/>
-    <col min="15" max="15" width="5.42857142857143" customWidth="1"/>
-    <col min="16" max="16" width="6.71428571428571" customWidth="1"/>
-    <col min="17" max="17" width="23.7142857142857" customWidth="1"/>
-    <col min="18" max="18" width="20.8571428571429" customWidth="1"/>
-    <col min="19" max="19" width="21.7142857142857" customWidth="1"/>
-    <col min="20" max="20" width="14.8571428571429" customWidth="1"/>
-    <col min="21" max="21" width="28" customWidth="1"/>
-    <col min="22" max="22" width="11.2857142857143" customWidth="1"/>
-    <col min="23" max="23" width="12.5714285714286" customWidth="1"/>
-    <col min="24" max="24" width="10.7142857142857" customWidth="1"/>
-    <col min="25" max="25" width="12.5714285714286" customWidth="1"/>
-    <col min="26" max="26" width="12" customWidth="1"/>
-    <col min="27" max="27" width="12.8571428571429" customWidth="1"/>
-    <col min="28" max="28" width="14.4285714285714" customWidth="1"/>
-    <col min="29" max="29" width="16.5714285714286" customWidth="1"/>
-    <col min="30" max="30" width="5.28571428571429" customWidth="1"/>
+    <col min="9" max="9" width="17.7142857142857" customWidth="1"/>
+    <col min="10" max="10" width="6.57142857142857" customWidth="1"/>
+    <col min="11" max="11" width="8.28571428571429" customWidth="1"/>
+    <col min="12" max="12" width="18.5714285714286" customWidth="1"/>
+    <col min="13" max="13" width="4.57142857142857" customWidth="1"/>
+    <col min="14" max="14" width="5.42857142857143" customWidth="1"/>
+    <col min="15" max="15" width="6.71428571428571" customWidth="1"/>
+    <col min="16" max="16" width="23.7142857142857" customWidth="1"/>
+    <col min="17" max="17" width="20.8571428571429" customWidth="1"/>
+    <col min="18" max="18" width="21.7142857142857" customWidth="1"/>
+    <col min="19" max="19" width="14.8571428571429" customWidth="1"/>
+    <col min="20" max="20" width="28" customWidth="1"/>
+    <col min="21" max="21" width="11.2857142857143" customWidth="1"/>
+    <col min="22" max="22" width="12.5714285714286" customWidth="1"/>
+    <col min="23" max="23" width="10.7142857142857" customWidth="1"/>
+    <col min="24" max="24" width="12.5714285714286" customWidth="1"/>
+    <col min="25" max="25" width="12" customWidth="1"/>
+    <col min="26" max="26" width="12.8571428571429" customWidth="1"/>
+    <col min="27" max="27" width="14.4285714285714" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30">
+    <row r="1" spans="1:27">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1564,114 +1537,96 @@
       <c r="AA1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:27">
+      <c r="A2" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>29</v>
       </c>
+      <c r="D2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="W2" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="X2" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y2" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z2" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA2" s="2" t="s">
+        <v>53</v>
+      </c>
     </row>
-    <row r="2" spans="1:30">
-      <c r="A2" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="S2" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="T2" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="U2" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="V2" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="W2" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="X2" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="Y2" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z2" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="AA2" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="AB2" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="AC2" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="AD2" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27">
+    <row r="3" spans="1:26">
       <c r="A3" t="s">
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C3" t="s">
         <v>2</v>
@@ -1680,58 +1635,58 @@
         <v>3</v>
       </c>
       <c r="E3" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="F3" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="G3" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="H3" t="s">
         <v>7</v>
       </c>
       <c r="I3" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="J3" t="s">
-        <v>65</v>
+        <v>9</v>
       </c>
       <c r="K3" t="s">
         <v>10</v>
       </c>
       <c r="L3" t="s">
-        <v>11</v>
+        <v>59</v>
       </c>
       <c r="M3" t="s">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="N3" t="s">
         <v>13</v>
       </c>
       <c r="O3" t="s">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="P3" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="Q3" t="s">
-        <v>68</v>
+        <v>16</v>
       </c>
       <c r="R3" t="s">
-        <v>17</v>
+        <v>62</v>
       </c>
       <c r="S3" t="s">
-        <v>69</v>
-      </c>
-      <c r="T3" t="s">
-        <v>19</v>
+        <v>18</v>
+      </c>
+      <c r="U3" t="s">
+        <v>63</v>
       </c>
       <c r="V3" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="W3" t="s">
-        <v>71</v>
+        <v>22</v>
       </c>
       <c r="X3" t="s">
         <v>23</v>
@@ -1742,93 +1697,87 @@
       <c r="Z3" t="s">
         <v>25</v>
       </c>
-      <c r="AA3" t="s">
-        <v>26</v>
-      </c>
     </row>
-    <row r="4" spans="1:27">
+    <row r="4" spans="1:26">
       <c r="A4" t="s">
         <v>0</v>
       </c>
       <c r="B4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" t="s">
+        <v>66</v>
+      </c>
+      <c r="F4" t="s">
+        <v>67</v>
+      </c>
+      <c r="G4" t="s">
+        <v>68</v>
+      </c>
+      <c r="H4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I4" t="s">
+        <v>69</v>
+      </c>
+      <c r="J4" t="s">
+        <v>36</v>
+      </c>
+      <c r="K4" t="s">
+        <v>37</v>
+      </c>
+      <c r="L4" t="s">
+        <v>70</v>
+      </c>
+      <c r="M4" t="s">
+        <v>39</v>
+      </c>
+      <c r="N4" t="s">
+        <v>40</v>
+      </c>
+      <c r="O4" t="s">
+        <v>71</v>
+      </c>
+      <c r="P4" t="s">
         <v>72</v>
       </c>
-      <c r="C4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D4" t="s">
-        <v>33</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="Q4" t="s">
+        <v>43</v>
+      </c>
+      <c r="R4" t="s">
         <v>73</v>
       </c>
-      <c r="F4" t="s">
+      <c r="S4" t="s">
+        <v>45</v>
+      </c>
+      <c r="U4" t="s">
         <v>74</v>
       </c>
-      <c r="G4" t="s">
+      <c r="V4" t="s">
         <v>75</v>
       </c>
-      <c r="H4" t="s">
-        <v>37</v>
-      </c>
-      <c r="I4" t="s">
+      <c r="W4" t="s">
+        <v>49</v>
+      </c>
+      <c r="X4" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="17:17">
+      <c r="Q5" t="s">
         <v>76</v>
-      </c>
-      <c r="J4" t="s">
-        <v>77</v>
-      </c>
-      <c r="K4" t="s">
-        <v>40</v>
-      </c>
-      <c r="L4" t="s">
-        <v>41</v>
-      </c>
-      <c r="M4" t="s">
-        <v>78</v>
-      </c>
-      <c r="N4" t="s">
-        <v>43</v>
-      </c>
-      <c r="O4" t="s">
-        <v>44</v>
-      </c>
-      <c r="P4" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>80</v>
-      </c>
-      <c r="R4" t="s">
-        <v>47</v>
-      </c>
-      <c r="S4" t="s">
-        <v>81</v>
-      </c>
-      <c r="T4" t="s">
-        <v>49</v>
-      </c>
-      <c r="V4" t="s">
-        <v>82</v>
-      </c>
-      <c r="W4" t="s">
-        <v>83</v>
-      </c>
-      <c r="X4" t="s">
-        <v>53</v>
-      </c>
-      <c r="Y4" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>55</v>
-      </c>
-      <c r="AA4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="5" spans="18:18">
-      <c r="R5" t="s">
-        <v>84</v>
       </c>
     </row>
   </sheetData>
